--- a/HousePrices-AdvancedRegressionTechniques/notebooks/Performance_Comparison.xlsx
+++ b/HousePrices-AdvancedRegressionTechniques/notebooks/Performance_Comparison.xlsx
@@ -67,6 +67,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -88,12 +89,14 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -138,20 +141,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -278,435 +285,597 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="18.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="1" style="1" width="15.32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3" t="s">
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="P2" s="2" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>0.074</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="G3" s="1" t="n">
+      <c r="C3" s="2" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>0.119</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.119</v>
       </c>
-      <c r="J3" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="2" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.133</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="O3" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.071</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>0.133</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>0.134</v>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="N4" s="2" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="O4" s="2" t="n">
         <v>0.133</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>0.072</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="E4" s="1" t="n">
+      <c r="P4" s="2" t="n">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>0.062</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L4" s="1" t="n">
+      <c r="D5" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>0.134</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="I6" s="2" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <v>0.135</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.133</v>
       </c>
-      <c r="O4" s="1" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>0.131</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>0.072</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0.069</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0.137</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>0.142</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="O7" s="1" t="n">
+      <c r="L7" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P7" s="2" t="n">
         <v>0.153</v>
       </c>
-      <c r="P7" s="1" t="n">
-        <v>0.15</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0.18</v>
+      <c r="G8" s="2" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B9" s="2" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>0.205</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="O9" s="1" t="n">
+      <c r="D9" s="2" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>0.233</v>
       </c>
-      <c r="P9" s="1" t="n">
-        <v>0.228</v>
-      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="J14" s="0"/>
+      <c r="K14" s="0"/>
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
+      <c r="O14" s="0"/>
+      <c r="P14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0"/>
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="0"/>
+      <c r="M15" s="0"/>
+      <c r="N15" s="0"/>
+      <c r="O15" s="0"/>
+      <c r="P15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
+      <c r="O16" s="0"/>
+      <c r="P16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+      <c r="I17" s="0"/>
+      <c r="J17" s="0"/>
+      <c r="K17" s="0"/>
+      <c r="L17" s="0"/>
+      <c r="M17" s="0"/>
+      <c r="N17" s="0"/>
+      <c r="O17" s="0"/>
+      <c r="P17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
+      <c r="O18" s="0"/>
+      <c r="P18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+      <c r="C19" s="0"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
+      <c r="O19" s="0"/>
+      <c r="P19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/HousePrices-AdvancedRegressionTechniques/notebooks/Performance_Comparison.xlsx
+++ b/HousePrices-AdvancedRegressionTechniques/notebooks/Performance_Comparison.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">Train</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">SVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance comparison of models based on feature counts</t>
   </si>
 </sst>
 </file>
@@ -62,7 +65,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -98,6 +101,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -141,7 +151,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -160,6 +170,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -715,149 +729,25 @@
         <v>0.222</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0"/>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-      <c r="I12" s="0"/>
-      <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
-      <c r="N12" s="0"/>
-      <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0"/>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
-      <c r="I14" s="0"/>
-      <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
-      <c r="N14" s="0"/>
-      <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0"/>
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
-      <c r="N15" s="0"/>
-      <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-      <c r="D16" s="0"/>
-      <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0"/>
-      <c r="K16" s="0"/>
-      <c r="L16" s="0"/>
-      <c r="M16" s="0"/>
-      <c r="N16" s="0"/>
-      <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-      <c r="D17" s="0"/>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
-      <c r="I17" s="0"/>
-      <c r="J17" s="0"/>
-      <c r="K17" s="0"/>
-      <c r="L17" s="0"/>
-      <c r="M17" s="0"/>
-      <c r="N17" s="0"/>
-      <c r="O17" s="0"/>
-      <c r="P17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
-      <c r="B18" s="0"/>
-      <c r="C18" s="0"/>
-      <c r="D18" s="0"/>
-      <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
-      <c r="I18" s="0"/>
-      <c r="J18" s="0"/>
-      <c r="K18" s="0"/>
-      <c r="L18" s="0"/>
-      <c r="M18" s="0"/>
-      <c r="N18" s="0"/>
-      <c r="O18" s="0"/>
-      <c r="P18" s="0"/>
-    </row>
-    <row r="19" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-      <c r="B19" s="0"/>
-      <c r="C19" s="0"/>
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
-      <c r="K19" s="0"/>
-      <c r="L19" s="0"/>
-      <c r="M19" s="0"/>
-      <c r="N19" s="0"/>
-      <c r="O19" s="0"/>
-      <c r="P19" s="0"/>
+    <row r="10" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -878,10 +768,11 @@
       <c r="P20" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:P1"/>
+    <mergeCell ref="A10:P10"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
